--- a/TestData/data.xlsx
+++ b/TestData/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java Student\Hybrid_Framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936A3B23-DAA1-44A0-BA15-63B34E95E71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5084871E-C0F0-49C1-808A-28B12C37F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Vishal@gmail.com</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>Vishal3@gamail.com</t>
+  </si>
+  <si>
+    <t>Seleium</t>
   </si>
 </sst>
 </file>
@@ -544,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -576,6 +579,11 @@
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/data.xlsx
+++ b/TestData/data.xlsx
@@ -1,34 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java Student\Hybrid_Framework\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationProjects\workspace\automation-testing-framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5084871E-C0F0-49C1-808A-28B12C37F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C86A58-D1AD-486D-B781-C61B86013F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Orrange HRM" sheetId="3" r:id="rId3"/>
     <sheet name="eCart" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>Vishal@gmail.com</t>
   </si>
@@ -199,6 +211,12 @@
   </si>
   <si>
     <t>Seleium</t>
+  </si>
+  <si>
+    <t>vishal@gmal.com</t>
+  </si>
+  <si>
+    <t>Solapur,nadre</t>
   </si>
 </sst>
 </file>
@@ -548,12 +566,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,27 +579,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>8788053005</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -598,19 +616,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B1AD8D9-BF5F-4103-8CB5-DCB2D558A359}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -623,19 +641,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D63FCCA-6D03-42BC-92B8-47CBC4A89FC7}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -643,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -651,13 +669,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -665,7 +683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -673,7 +691,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -681,7 +699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -689,13 +707,13 @@
         <v>11223</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -703,7 +721,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -711,7 +729,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -732,18 +750,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD962801-2490-4282-BF4B-921C341A2F36}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -755,7 +773,7 @@
         <v>1,1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -767,13 +785,13 @@
         <v>2,1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C4" t="str">
         <f t="shared" si="0"/>
         <v>3,1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -785,7 +803,7 @@
         <v>4,1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -797,7 +815,7 @@
         <v>5,1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -809,7 +827,7 @@
         <v>6,1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -821,7 +839,7 @@
         <v>7,1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -833,7 +851,7 @@
         <v>8,1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -845,7 +863,7 @@
         <v>9,1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -857,13 +875,13 @@
         <v>10,1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C12" t="str">
         <f t="shared" si="0"/>
         <v>11,1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -875,7 +893,7 @@
         <v>12,1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -887,7 +905,7 @@
         <v>13,1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -899,7 +917,7 @@
         <v>14,1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -911,7 +929,7 @@
         <v>15,1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -923,7 +941,7 @@
         <v>16,1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -935,7 +953,7 @@
         <v>17,1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -947,7 +965,7 @@
         <v>18,1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -959,7 +977,7 @@
         <v>19,1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -971,7 +989,7 @@
         <v>20,1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -991,4 +1009,45 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F7BD79-BC4E-4621-8B6C-ECB7521F3699}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>8788954007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{A25B5658-7D4D-4AD6-AC4F-232910783BB5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestData/data.xlsx
+++ b/TestData/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationProjects\workspace\automation-testing-framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C86A58-D1AD-486D-B781-C61B86013F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0154170F-4B50-4989-86BB-D4D5D8C08921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Orrange HRM" sheetId="3" r:id="rId3"/>
     <sheet name="eCart" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
+    <sheet name="DataEntryForm" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
   <si>
     <t>Vishal@gmail.com</t>
   </si>
@@ -217,6 +216,9 @@
   </si>
   <si>
     <t>Solapur,nadre</t>
+  </si>
+  <si>
+    <t>At Madre tel south solapur, Solapur</t>
   </si>
 </sst>
 </file>
@@ -1050,4 +1052,40 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0C28AF-5DB0-43BF-A8DF-14D3D1FD374B}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>8788053005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{4E060496-D1A1-4014-9053-653ED3AB9A5B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>